--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/50.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/50.xlsx
@@ -426,13 +426,13 @@
         <v>-21.4713248739941</v>
       </c>
       <c r="E2">
-        <v>-22.91573344853241</v>
+        <v>-26.15832009088072</v>
       </c>
       <c r="F2">
-        <v>0.6283836255355441</v>
+        <v>-1.377715960561561</v>
       </c>
       <c r="G2">
-        <v>-15.23547105331211</v>
+        <v>-18.35950542271907</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.33420078257868</v>
       </c>
       <c r="E3">
-        <v>-23.56960886744795</v>
+        <v>-26.87811650592592</v>
       </c>
       <c r="F3">
-        <v>0.7804917615072005</v>
+        <v>-1.438270446073608</v>
       </c>
       <c r="G3">
-        <v>-16.3039165206565</v>
+        <v>-18.01932038419464</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.1931000179995</v>
       </c>
       <c r="E4">
-        <v>-24.16158910362665</v>
+        <v>-27.14316356112086</v>
       </c>
       <c r="F4">
-        <v>0.8150429658779678</v>
+        <v>-1.278242289363786</v>
       </c>
       <c r="G4">
-        <v>-14.67830127323446</v>
+        <v>-17.2190688320777</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.04047065388376</v>
       </c>
       <c r="E5">
-        <v>-24.95875449709289</v>
+        <v>-27.94514725093126</v>
       </c>
       <c r="F5">
-        <v>0.7111176482575474</v>
+        <v>-1.216547970305487</v>
       </c>
       <c r="G5">
-        <v>-15.20943030210021</v>
+        <v>-16.89185285570336</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.86888635013797</v>
       </c>
       <c r="E6">
-        <v>-23.48752121911091</v>
+        <v>-27.88539856487406</v>
       </c>
       <c r="F6">
-        <v>0.7411675041615023</v>
+        <v>-1.266506808368325</v>
       </c>
       <c r="G6">
-        <v>-14.15018153026392</v>
+        <v>-16.90580349460585</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.67545612926145</v>
       </c>
       <c r="E7">
-        <v>-23.80298377543324</v>
+        <v>-28.49106837797795</v>
       </c>
       <c r="F7">
-        <v>0.6088151023792113</v>
+        <v>-1.295753147891564</v>
       </c>
       <c r="G7">
-        <v>-13.96905330744654</v>
+        <v>-16.41911853960482</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.43368855138512</v>
       </c>
       <c r="E8">
-        <v>-25.60925620287271</v>
+        <v>-29.26632954266909</v>
       </c>
       <c r="F8">
-        <v>0.4888716442908569</v>
+        <v>-1.18281353619388</v>
       </c>
       <c r="G8">
-        <v>-13.97001171038016</v>
+        <v>-16.08883534278835</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.1408265305828</v>
       </c>
       <c r="E9">
-        <v>-27.27405910231257</v>
+        <v>-29.3252585749309</v>
       </c>
       <c r="F9">
-        <v>1.134587348242683</v>
+        <v>-1.102677273647056</v>
       </c>
       <c r="G9">
-        <v>-12.35017336492416</v>
+        <v>-15.69883983608005</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.81636796988767</v>
       </c>
       <c r="E10">
-        <v>-27.90168748587965</v>
+        <v>-30.0923458440382</v>
       </c>
       <c r="F10">
-        <v>0.5314977741041138</v>
+        <v>-1.009708771663464</v>
       </c>
       <c r="G10">
-        <v>-11.39403815499955</v>
+        <v>-15.4430538455338</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.47635106786725</v>
       </c>
       <c r="E11">
-        <v>-26.07870046087787</v>
+        <v>-30.5768767131999</v>
       </c>
       <c r="F11">
-        <v>0.81995849804618</v>
+        <v>-1.166313285897516</v>
       </c>
       <c r="G11">
-        <v>-12.90774868683037</v>
+        <v>-14.63227310332921</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.13314997685038</v>
       </c>
       <c r="E12">
-        <v>-26.94433185286607</v>
+        <v>-30.82841985890397</v>
       </c>
       <c r="F12">
-        <v>1.222646116629881</v>
+        <v>-0.994861114335686</v>
       </c>
       <c r="G12">
-        <v>-11.46083503234542</v>
+        <v>-14.22675941440557</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.81398648748911</v>
       </c>
       <c r="E13">
-        <v>-28.53616745062034</v>
+        <v>-31.52955443256355</v>
       </c>
       <c r="F13">
-        <v>0.8122513677305335</v>
+        <v>-1.052247094532025</v>
       </c>
       <c r="G13">
-        <v>-11.82302195652385</v>
+        <v>-13.71833245157538</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.56672151281716</v>
       </c>
       <c r="E14">
-        <v>-28.36722819929019</v>
+        <v>-32.00987834937213</v>
       </c>
       <c r="F14">
-        <v>1.201244416411153</v>
+        <v>-0.7890573749471629</v>
       </c>
       <c r="G14">
-        <v>-10.93260769664485</v>
+        <v>-13.63341364794753</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.40433105343416</v>
       </c>
       <c r="E15">
-        <v>-30.1430579602131</v>
+        <v>-32.92904536107902</v>
       </c>
       <c r="F15">
-        <v>2.076267128071133</v>
+        <v>-0.5063148711866216</v>
       </c>
       <c r="G15">
-        <v>-10.70285914676497</v>
+        <v>-13.58712891076298</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.32949228048854</v>
       </c>
       <c r="E16">
-        <v>-28.9991858040086</v>
+        <v>-33.30649819809235</v>
       </c>
       <c r="F16">
-        <v>1.736709389254782</v>
+        <v>-0.9354133276737795</v>
       </c>
       <c r="G16">
-        <v>-10.63633042360778</v>
+        <v>-13.25414099824093</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.34809898295233</v>
       </c>
       <c r="E17">
-        <v>-30.44390033820167</v>
+        <v>-33.32425887315043</v>
       </c>
       <c r="F17">
-        <v>1.32869536827108</v>
+        <v>-0.4094580126142894</v>
       </c>
       <c r="G17">
-        <v>-9.952967613391419</v>
+        <v>-12.59915287384166</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.46388943817933</v>
       </c>
       <c r="E18">
-        <v>-32.05732317155049</v>
+        <v>-35.38646933031842</v>
       </c>
       <c r="F18">
-        <v>2.461547434052405</v>
+        <v>-0.3787396642162753</v>
       </c>
       <c r="G18">
-        <v>-10.00023227205559</v>
+        <v>-12.26222872267342</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-18.64537375681812</v>
       </c>
       <c r="E19">
-        <v>-31.35619539060192</v>
+        <v>-35.52547763269487</v>
       </c>
       <c r="F19">
-        <v>2.231425312819897</v>
+        <v>-0.4554995012292887</v>
       </c>
       <c r="G19">
-        <v>-9.038141390705837</v>
+        <v>-11.71743872763987</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.86707148386143</v>
       </c>
       <c r="E20">
-        <v>-32.13057123862456</v>
+        <v>-35.19902446995592</v>
       </c>
       <c r="F20">
-        <v>2.204862883681728</v>
+        <v>-0.2146889553984584</v>
       </c>
       <c r="G20">
-        <v>-9.126794489701981</v>
+        <v>-11.64542111997857</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.11476207570866</v>
       </c>
       <c r="E21">
-        <v>-32.60849959268308</v>
+        <v>-35.97812804484258</v>
       </c>
       <c r="F21">
-        <v>2.271483503684475</v>
+        <v>-0.05628522716552576</v>
       </c>
       <c r="G21">
-        <v>-8.869210872927907</v>
+        <v>-11.62349537687197</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-19.36978844995319</v>
       </c>
       <c r="E22">
-        <v>-34.0034756326129</v>
+        <v>-37.14504334103511</v>
       </c>
       <c r="F22">
-        <v>2.01054445833302</v>
+        <v>-0.1306684780999074</v>
       </c>
       <c r="G22">
-        <v>-8.507411282577577</v>
+        <v>-11.81216998824612</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.59216001020361</v>
       </c>
       <c r="E23">
-        <v>-34.50862237969451</v>
+        <v>-36.92557084825336</v>
       </c>
       <c r="F23">
-        <v>2.561238137509715</v>
+        <v>0.1576969835908369</v>
       </c>
       <c r="G23">
-        <v>-8.99438259976775</v>
+        <v>-11.45876263083784</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.76102237540361</v>
       </c>
       <c r="E24">
-        <v>-35.07896783130158</v>
+        <v>-37.2643573099522</v>
       </c>
       <c r="F24">
-        <v>3.327345446314809</v>
+        <v>-0.1674074007814682</v>
       </c>
       <c r="G24">
-        <v>-8.54900828727852</v>
+        <v>-10.97404248461437</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.87253547089168</v>
       </c>
       <c r="E25">
-        <v>-35.6795249972508</v>
+        <v>-37.09323080567634</v>
       </c>
       <c r="F25">
-        <v>2.999128057242784</v>
+        <v>-0.04238853561616125</v>
       </c>
       <c r="G25">
-        <v>-9.154311744224403</v>
+        <v>-11.30027026314523</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.91404137680852</v>
       </c>
       <c r="E26">
-        <v>-34.58357994570648</v>
+        <v>-37.8565775552533</v>
       </c>
       <c r="F26">
-        <v>2.237561858539836</v>
+        <v>-0.1605410633796631</v>
       </c>
       <c r="G26">
-        <v>-8.341943595433724</v>
+        <v>-11.5514976324839</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-19.87071576646328</v>
       </c>
       <c r="E27">
-        <v>-35.60732527190951</v>
+        <v>-37.25227307706273</v>
       </c>
       <c r="F27">
-        <v>2.671225447783822</v>
+        <v>-0.05449761031028443</v>
       </c>
       <c r="G27">
-        <v>-8.795041410666075</v>
+        <v>-11.15297416046644</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-19.74471147808906</v>
       </c>
       <c r="E28">
-        <v>-34.85185806710589</v>
+        <v>-37.44636347303148</v>
       </c>
       <c r="F28">
-        <v>2.851955334257007</v>
+        <v>0.2039430789543277</v>
       </c>
       <c r="G28">
-        <v>-8.402741764262441</v>
+        <v>-11.3400067412531</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-19.56061499357671</v>
       </c>
       <c r="E29">
-        <v>-35.4321525761078</v>
+        <v>-37.37631024436983</v>
       </c>
       <c r="F29">
-        <v>2.038922668818125</v>
+        <v>0.004799413484312584</v>
       </c>
       <c r="G29">
-        <v>-7.166693307901374</v>
+        <v>-11.30941730047024</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-19.32370675140973</v>
       </c>
       <c r="E30">
-        <v>-35.26510622691286</v>
+        <v>-37.40454075133364</v>
       </c>
       <c r="F30">
-        <v>1.963001139616745</v>
+        <v>-0.0657634069883577</v>
       </c>
       <c r="G30">
-        <v>-8.372867401316057</v>
+        <v>-10.96704068079881</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-19.04329268856894</v>
       </c>
       <c r="E31">
-        <v>-34.65787635451333</v>
+        <v>-36.98549614479686</v>
       </c>
       <c r="F31">
-        <v>2.379015532976685</v>
+        <v>0.1919748267186805</v>
       </c>
       <c r="G31">
-        <v>-8.711205155429571</v>
+        <v>-10.82554134335928</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-18.74257128468283</v>
       </c>
       <c r="E32">
-        <v>-34.59228593698623</v>
+        <v>-37.20999750796413</v>
       </c>
       <c r="F32">
-        <v>2.659320151470787</v>
+        <v>0.04115231695616889</v>
       </c>
       <c r="G32">
-        <v>-7.951521028350856</v>
+        <v>-11.26646297209819</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-18.45048359191057</v>
       </c>
       <c r="E33">
-        <v>-35.16481411306498</v>
+        <v>-36.72118949510218</v>
       </c>
       <c r="F33">
-        <v>1.82797559622562</v>
+        <v>-0.01371376960085357</v>
       </c>
       <c r="G33">
-        <v>-6.607413055042439</v>
+        <v>-11.23724740771413</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-18.16948204676161</v>
       </c>
       <c r="E34">
-        <v>-32.44028036872015</v>
+        <v>-36.16669596675897</v>
       </c>
       <c r="F34">
-        <v>2.320145118394529</v>
+        <v>-0.0942493052358271</v>
       </c>
       <c r="G34">
-        <v>-7.491454514758339</v>
+        <v>-11.70058474029944</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-17.90855799443324</v>
       </c>
       <c r="E35">
-        <v>-32.88034615160053</v>
+        <v>-36.14881302290268</v>
       </c>
       <c r="F35">
-        <v>1.6865600266893</v>
+        <v>-0.02325904718331227</v>
       </c>
       <c r="G35">
-        <v>-7.650764587199147</v>
+        <v>-11.63501607534864</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.68630335204937</v>
       </c>
       <c r="E36">
-        <v>-32.4995263941625</v>
+        <v>-35.53858530071007</v>
       </c>
       <c r="F36">
-        <v>2.349689670182777</v>
+        <v>-0.198003150803868</v>
       </c>
       <c r="G36">
-        <v>-7.334994822026843</v>
+        <v>-11.63256296110404</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.51274587720649</v>
       </c>
       <c r="E37">
-        <v>-31.88382601113162</v>
+        <v>-35.48105783115363</v>
       </c>
       <c r="F37">
-        <v>2.12677600208943</v>
+        <v>-0.05261887304073515</v>
       </c>
       <c r="G37">
-        <v>-7.64002848801529</v>
+        <v>-11.76678902999379</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.37465813839508</v>
       </c>
       <c r="E38">
-        <v>-30.75183204224924</v>
+        <v>-34.11656068553244</v>
       </c>
       <c r="F38">
-        <v>2.289642973888646</v>
+        <v>0.06756812506404232</v>
       </c>
       <c r="G38">
-        <v>-8.653588420864097</v>
+        <v>-12.14442958074953</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.26822450043734</v>
       </c>
       <c r="E39">
-        <v>-31.71931107890697</v>
+        <v>-34.01468360578188</v>
       </c>
       <c r="F39">
-        <v>2.795712501076531</v>
+        <v>-0.05832549607862094</v>
       </c>
       <c r="G39">
-        <v>-8.095804534588911</v>
+        <v>-11.86390719393385</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.20191173640396</v>
       </c>
       <c r="E40">
-        <v>-31.38465911397713</v>
+        <v>-34.10591650737742</v>
       </c>
       <c r="F40">
-        <v>1.691992460116859</v>
+        <v>0.3141308541399124</v>
       </c>
       <c r="G40">
-        <v>-7.659150199050121</v>
+        <v>-11.90561344663759</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.16511020130725</v>
       </c>
       <c r="E41">
-        <v>-30.72383928017083</v>
+        <v>-33.95592665553236</v>
       </c>
       <c r="F41">
-        <v>2.249442303830786</v>
+        <v>0.358885888178364</v>
       </c>
       <c r="G41">
-        <v>-7.76472018575194</v>
+        <v>-11.88666057342526</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.13852371162734</v>
       </c>
       <c r="E42">
-        <v>-28.90410596374355</v>
+        <v>-33.03863443206464</v>
       </c>
       <c r="F42">
-        <v>2.646995701251936</v>
+        <v>0.355027352816124</v>
       </c>
       <c r="G42">
-        <v>-8.547614547606486</v>
+        <v>-11.96789805041344</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.11346951540613</v>
       </c>
       <c r="E43">
-        <v>-30.35484110412982</v>
+        <v>-32.89085221129833</v>
       </c>
       <c r="F43">
-        <v>2.094595585225475</v>
+        <v>0.5414704892664171</v>
       </c>
       <c r="G43">
-        <v>-9.653717470460078</v>
+        <v>-11.61300756860356</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-17.09785379458934</v>
       </c>
       <c r="E44">
-        <v>-30.37962317813679</v>
+        <v>-32.17054634292727</v>
       </c>
       <c r="F44">
-        <v>3.091100033240807</v>
+        <v>0.1937094280601426</v>
       </c>
       <c r="G44">
-        <v>-8.322944374583846</v>
+        <v>-12.17814086597593</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-17.07713586260588</v>
       </c>
       <c r="E45">
-        <v>-28.23690777429745</v>
+        <v>-31.32651124348164</v>
       </c>
       <c r="F45">
-        <v>2.707622254728026</v>
+        <v>0.7378573480199154</v>
       </c>
       <c r="G45">
-        <v>-8.504663529779982</v>
+        <v>-12.35233184061576</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-17.04190816446474</v>
       </c>
       <c r="E46">
-        <v>-28.1691618031427</v>
+        <v>-31.13366164939099</v>
       </c>
       <c r="F46">
-        <v>3.270487964521457</v>
+        <v>0.4111707819082632</v>
       </c>
       <c r="G46">
-        <v>-8.600258842771977</v>
+        <v>-12.70283916013164</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.99816285186137</v>
       </c>
       <c r="E47">
-        <v>-27.5088740650323</v>
+        <v>-30.73932666127706</v>
       </c>
       <c r="F47">
-        <v>3.224029807102849</v>
+        <v>0.5487046217950652</v>
       </c>
       <c r="G47">
-        <v>-8.809819685953382</v>
+        <v>-12.61963521909314</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.95887757440458</v>
       </c>
       <c r="E48">
-        <v>-26.54395588042592</v>
+        <v>-30.32337273825052</v>
       </c>
       <c r="F48">
-        <v>2.906216712609985</v>
+        <v>0.5092138626014043</v>
       </c>
       <c r="G48">
-        <v>-10.16586217593087</v>
+        <v>-12.80509860129419</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.91544645596262</v>
       </c>
       <c r="E49">
-        <v>-26.80651227491663</v>
+        <v>-29.77977471836977</v>
       </c>
       <c r="F49">
-        <v>2.905860514626782</v>
+        <v>0.6568960315399029</v>
       </c>
       <c r="G49">
-        <v>-8.377565065436283</v>
+        <v>-12.99992751682584</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.87286597812613</v>
       </c>
       <c r="E50">
-        <v>-26.31550342368696</v>
+        <v>-29.56488051280978</v>
       </c>
       <c r="F50">
-        <v>3.237247237381918</v>
+        <v>0.5695786519782099</v>
       </c>
       <c r="G50">
-        <v>-9.824574725741865</v>
+        <v>-12.96366049044312</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.84772557529514</v>
       </c>
       <c r="E51">
-        <v>-25.67404508050046</v>
+        <v>-28.20669832419228</v>
       </c>
       <c r="F51">
-        <v>2.891345860994929</v>
+        <v>0.585262132015413</v>
       </c>
       <c r="G51">
-        <v>-10.27169700627583</v>
+        <v>-13.5403608339297</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.85014762215934</v>
       </c>
       <c r="E52">
-        <v>-25.78855207425841</v>
+        <v>-28.981710422813</v>
       </c>
       <c r="F52">
-        <v>3.084100328687151</v>
+        <v>0.5250249112186385</v>
       </c>
       <c r="G52">
-        <v>-11.27683822181827</v>
+        <v>-13.42211476835801</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.8714854705491</v>
       </c>
       <c r="E53">
-        <v>-24.73319120677083</v>
+        <v>-28.44986379298215</v>
       </c>
       <c r="F53">
-        <v>3.325942191934467</v>
+        <v>0.5813977980813533</v>
       </c>
       <c r="G53">
-        <v>-10.15993629941558</v>
+        <v>-13.6721635834847</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.91641002780761</v>
       </c>
       <c r="E54">
-        <v>-25.13414229540997</v>
+        <v>-28.17155283741875</v>
       </c>
       <c r="F54">
-        <v>3.289064931896638</v>
+        <v>0.7801885790377758</v>
       </c>
       <c r="G54">
-        <v>-10.18020014866145</v>
+        <v>-14.00581691566015</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-17.00068927672323</v>
       </c>
       <c r="E55">
-        <v>-24.84631701595644</v>
+        <v>-27.93604501817585</v>
       </c>
       <c r="F55">
-        <v>3.425979152966146</v>
+        <v>0.3290737737190126</v>
       </c>
       <c r="G55">
-        <v>-10.81735436424067</v>
+        <v>-13.84615592539218</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-17.12062863179204</v>
       </c>
       <c r="E56">
-        <v>-23.01410096092702</v>
+        <v>-26.84626774822997</v>
       </c>
       <c r="F56">
-        <v>3.32245145169907</v>
+        <v>0.8158348851150441</v>
       </c>
       <c r="G56">
-        <v>-11.62781563880072</v>
+        <v>-13.81761074647981</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-17.26432777426571</v>
       </c>
       <c r="E57">
-        <v>-24.46149182325863</v>
+        <v>-27.0037409033727</v>
       </c>
       <c r="F57">
-        <v>3.31039373578392</v>
+        <v>0.6742213357694546</v>
       </c>
       <c r="G57">
-        <v>-9.18462309918197</v>
+        <v>-13.78016351061235</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-17.4309780110482</v>
       </c>
       <c r="E58">
-        <v>-22.79559756158292</v>
+        <v>-26.68547069316562</v>
       </c>
       <c r="F58">
-        <v>3.046785690660645</v>
+        <v>0.572491191766453</v>
       </c>
       <c r="G58">
-        <v>-10.64074007026609</v>
+        <v>-13.9319917501344</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.62993186937534</v>
       </c>
       <c r="E59">
-        <v>-23.70983306509546</v>
+        <v>-26.64453781661028</v>
       </c>
       <c r="F59">
-        <v>2.929233729264173</v>
+        <v>0.7464939065615032</v>
       </c>
       <c r="G59">
-        <v>-10.97341679150745</v>
+        <v>-14.16330287750882</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.84517808649758</v>
       </c>
       <c r="E60">
-        <v>-22.43419816492678</v>
+        <v>-26.39604686238739</v>
       </c>
       <c r="F60">
-        <v>2.996475624819019</v>
+        <v>0.6356003623487333</v>
       </c>
       <c r="G60">
-        <v>-11.59761353184595</v>
+        <v>-14.6375285943728</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-18.0647965899576</v>
       </c>
       <c r="E61">
-        <v>-22.63923388257207</v>
+        <v>-26.89962222898835</v>
       </c>
       <c r="F61">
-        <v>3.072160240943199</v>
+        <v>0.7236889519624328</v>
       </c>
       <c r="G61">
-        <v>-11.5588735279454</v>
+        <v>-14.52136817249085</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-18.2891233402559</v>
       </c>
       <c r="E62">
-        <v>-22.31829187270046</v>
+        <v>-26.1528134664874</v>
       </c>
       <c r="F62">
-        <v>3.374138264164148</v>
+        <v>0.5246455189481564</v>
       </c>
       <c r="G62">
-        <v>-11.89158335464215</v>
+        <v>-14.99776395195582</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-18.52023794712113</v>
       </c>
       <c r="E63">
-        <v>-22.40311924781214</v>
+        <v>-26.46015194043997</v>
       </c>
       <c r="F63">
-        <v>2.739507772796585</v>
+        <v>0.6854349453011516</v>
       </c>
       <c r="G63">
-        <v>-10.2631889042399</v>
+        <v>-14.52279170707274</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-18.73523763971265</v>
       </c>
       <c r="E64">
-        <v>-22.01053677913918</v>
+        <v>-26.20717779694948</v>
       </c>
       <c r="F64">
-        <v>3.049138254084595</v>
+        <v>0.7288828155779856</v>
       </c>
       <c r="G64">
-        <v>-12.53491835874319</v>
+        <v>-14.42747779045158</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.92740289387032</v>
       </c>
       <c r="E65">
-        <v>-23.58376034872192</v>
+        <v>-25.29088636623746</v>
       </c>
       <c r="F65">
-        <v>3.483608673178908</v>
+        <v>0.5392637185053593</v>
       </c>
       <c r="G65">
-        <v>-11.36980496165208</v>
+        <v>-14.72478133260583</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-19.10034863638891</v>
       </c>
       <c r="E66">
-        <v>-22.6026438125901</v>
+        <v>-25.32032597576132</v>
       </c>
       <c r="F66">
-        <v>3.394053873262254</v>
+        <v>0.7040889508447936</v>
       </c>
       <c r="G66">
-        <v>-11.50233272068019</v>
+        <v>-14.95366086428165</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-19.2509343140434</v>
       </c>
       <c r="E67">
-        <v>-22.21559513915451</v>
+        <v>-25.93014387105624</v>
       </c>
       <c r="F67">
-        <v>2.924512035068215</v>
+        <v>0.5786766111631568</v>
       </c>
       <c r="G67">
-        <v>-11.18499706746781</v>
+        <v>-14.56794092713732</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-19.36109955833592</v>
       </c>
       <c r="E68">
-        <v>-20.55936011253717</v>
+        <v>-24.97608949559426</v>
       </c>
       <c r="F68">
-        <v>3.196667175053576</v>
+        <v>0.5845745870710893</v>
       </c>
       <c r="G68">
-        <v>-11.12450677937425</v>
+        <v>-14.68247256061394</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-19.42756935590531</v>
       </c>
       <c r="E69">
-        <v>-22.03537093059725</v>
+        <v>-25.28357288071507</v>
       </c>
       <c r="F69">
-        <v>2.846324092652775</v>
+        <v>0.7459107359099323</v>
       </c>
       <c r="G69">
-        <v>-12.19445523439346</v>
+        <v>-15.18618861714175</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-19.46152173625854</v>
       </c>
       <c r="E70">
-        <v>-22.93431830585989</v>
+        <v>-25.12344603980385</v>
       </c>
       <c r="F70">
-        <v>2.937805675148342</v>
+        <v>0.6073853402419793</v>
       </c>
       <c r="G70">
-        <v>-12.38020332351089</v>
+        <v>-14.69654568970139</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-19.45611946234941</v>
       </c>
       <c r="E71">
-        <v>-22.7563855051505</v>
+        <v>-25.0430067560056</v>
       </c>
       <c r="F71">
-        <v>2.992284085760854</v>
+        <v>0.5047439920958982</v>
       </c>
       <c r="G71">
-        <v>-12.01624194692341</v>
+        <v>-14.47035597627622</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-19.4009628516695</v>
       </c>
       <c r="E72">
-        <v>-23.04589084846087</v>
+        <v>-25.42161435389089</v>
       </c>
       <c r="F72">
-        <v>2.657144858671036</v>
+        <v>0.2912157266762697</v>
       </c>
       <c r="G72">
-        <v>-11.81685109963865</v>
+        <v>-14.31609779632834</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-19.29797389730804</v>
       </c>
       <c r="E73">
-        <v>-22.65364348686448</v>
+        <v>-25.4863896460966</v>
       </c>
       <c r="F73">
-        <v>3.018153999750282</v>
+        <v>0.1380787583903362</v>
       </c>
       <c r="G73">
-        <v>-11.97608502953205</v>
+        <v>-14.51570217380039</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-19.16200640269812</v>
       </c>
       <c r="E74">
-        <v>-22.91901206371396</v>
+        <v>-25.73127593500939</v>
       </c>
       <c r="F74">
-        <v>2.770385996103339</v>
+        <v>0.1927609473839372</v>
       </c>
       <c r="G74">
-        <v>-11.93562354195108</v>
+        <v>-14.38348891659851</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.98608258739718</v>
       </c>
       <c r="E75">
-        <v>-22.46572087249418</v>
+        <v>-25.26075390019042</v>
       </c>
       <c r="F75">
-        <v>2.83859376804985</v>
+        <v>0.4366356242377228</v>
       </c>
       <c r="G75">
-        <v>-11.92185829359879</v>
+        <v>-14.49765804533859</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.76911384842981</v>
       </c>
       <c r="E76">
-        <v>-24.20173402570465</v>
+        <v>-26.3877869257974</v>
       </c>
       <c r="F76">
-        <v>3.069837498745749</v>
+        <v>0.3565954523096234</v>
       </c>
       <c r="G76">
-        <v>-11.69525476198122</v>
+        <v>-14.5181602538633</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.52396627219322</v>
       </c>
       <c r="E77">
-        <v>-22.63610017855877</v>
+        <v>-25.87519536744717</v>
       </c>
       <c r="F77">
-        <v>2.625206325088698</v>
+        <v>0.3812195017252415</v>
       </c>
       <c r="G77">
-        <v>-12.01793694623952</v>
+        <v>-14.67818871468613</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-18.26622959890915</v>
       </c>
       <c r="E78">
-        <v>-25.15735072469927</v>
+        <v>-26.57581822354388</v>
       </c>
       <c r="F78">
-        <v>2.583463234926825</v>
+        <v>0.2696972266537469</v>
       </c>
       <c r="G78">
-        <v>-11.09840312779709</v>
+        <v>-14.44030780968903</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.98914192599835</v>
       </c>
       <c r="E79">
-        <v>-24.50659542437502</v>
+        <v>-26.84765346127632</v>
       </c>
       <c r="F79">
-        <v>2.430636076049539</v>
+        <v>0.04542503601980874</v>
       </c>
       <c r="G79">
-        <v>-10.9097914167882</v>
+        <v>-14.34774992222931</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.699422377961</v>
       </c>
       <c r="E80">
-        <v>-24.55233301185249</v>
+        <v>-27.20427078938036</v>
       </c>
       <c r="F80">
-        <v>2.448959562999464</v>
+        <v>0.4211691764600533</v>
       </c>
       <c r="G80">
-        <v>-10.81183237428116</v>
+        <v>-14.17949641101416</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.41632738910192</v>
       </c>
       <c r="E81">
-        <v>-25.8902706574187</v>
+        <v>-26.91644098145283</v>
       </c>
       <c r="F81">
-        <v>2.81642499961613</v>
+        <v>0.01071064327068985</v>
       </c>
       <c r="G81">
-        <v>-11.52858203626107</v>
+        <v>-14.21619215304422</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.14966077408179</v>
       </c>
       <c r="E82">
-        <v>-25.76355489773607</v>
+        <v>-28.15736059987871</v>
       </c>
       <c r="F82">
-        <v>2.662229377789419</v>
+        <v>-0.06859890860814041</v>
       </c>
       <c r="G82">
-        <v>-11.71801145201817</v>
+        <v>-13.64868684979296</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.89479641384883</v>
       </c>
       <c r="E83">
-        <v>-26.13265722867926</v>
+        <v>-28.72905327250305</v>
       </c>
       <c r="F83">
-        <v>3.009532351821945</v>
+        <v>-0.2340851781350088</v>
       </c>
       <c r="G83">
-        <v>-10.54094036443922</v>
+        <v>-13.86514024878713</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.65667048457942</v>
       </c>
       <c r="E84">
-        <v>-27.76254106504596</v>
+        <v>-29.99870379427059</v>
       </c>
       <c r="F84">
-        <v>3.050914273796197</v>
+        <v>-0.2531069788054939</v>
       </c>
       <c r="G84">
-        <v>-10.7641307236058</v>
+        <v>-13.32247396871703</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.45730852873436</v>
       </c>
       <c r="E85">
-        <v>-28.00060294362919</v>
+        <v>-30.51609100659494</v>
       </c>
       <c r="F85">
-        <v>2.637847211655418</v>
+        <v>-0.01525950317447745</v>
       </c>
       <c r="G85">
-        <v>-9.92489087667286</v>
+        <v>-13.44527203440521</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.29635330190448</v>
       </c>
       <c r="E86">
-        <v>-29.15279164234878</v>
+        <v>-30.20354252329655</v>
       </c>
       <c r="F86">
-        <v>2.482289753818505</v>
+        <v>-0.2099921122245852</v>
       </c>
       <c r="G86">
-        <v>-10.92501992626884</v>
+        <v>-12.97984243703908</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.16919745576381</v>
       </c>
       <c r="E87">
-        <v>-29.87965926955695</v>
+        <v>-31.85350561341327</v>
       </c>
       <c r="F87">
-        <v>1.891653855213624</v>
+        <v>-0.4327293380611359</v>
       </c>
       <c r="G87">
-        <v>-10.55181881708126</v>
+        <v>-13.32941949325842</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.08293717423782</v>
       </c>
       <c r="E88">
-        <v>-31.2539877322488</v>
+        <v>-32.76062235578574</v>
       </c>
       <c r="F88">
-        <v>2.384550683962191</v>
+        <v>-0.07945714852403633</v>
       </c>
       <c r="G88">
-        <v>-10.37578386857606</v>
+        <v>-13.51374404779396</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.05504401641337</v>
       </c>
       <c r="E89">
-        <v>-33.7042725622151</v>
+        <v>-33.73013467727291</v>
       </c>
       <c r="F89">
-        <v>2.272368200070665</v>
+        <v>-0.3203670984432025</v>
       </c>
       <c r="G89">
-        <v>-9.378064896132663</v>
+        <v>-12.77284726665061</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.07756046476355</v>
       </c>
       <c r="E90">
-        <v>-33.30391696790798</v>
+        <v>-34.48183645593915</v>
       </c>
       <c r="F90">
-        <v>2.229047898373862</v>
+        <v>-0.4585677740892581</v>
       </c>
       <c r="G90">
-        <v>-10.19633243707432</v>
+        <v>-13.18312979642356</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.14938924457387</v>
       </c>
       <c r="E91">
-        <v>-33.79401559586211</v>
+        <v>-35.87696419974822</v>
       </c>
       <c r="F91">
-        <v>2.224004797625619</v>
+        <v>-0.8284893200552249</v>
       </c>
       <c r="G91">
-        <v>-8.659458018105225</v>
+        <v>-13.0957479469145</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.2821074395054</v>
       </c>
       <c r="E92">
-        <v>-36.62746593280243</v>
+        <v>-36.51416577736752</v>
       </c>
       <c r="F92">
-        <v>2.341772134546819</v>
+        <v>-0.691591666333773</v>
       </c>
       <c r="G92">
-        <v>-9.194872548171553</v>
+        <v>-13.11705792855079</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.48590091686887</v>
       </c>
       <c r="E93">
-        <v>-37.08119865023797</v>
+        <v>-38.52893367659414</v>
       </c>
       <c r="F93">
-        <v>2.063101056571037</v>
+        <v>-0.8472816629551345</v>
       </c>
       <c r="G93">
-        <v>-8.878950497904443</v>
+        <v>-12.61548379498689</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.74314901792397</v>
       </c>
       <c r="E94">
-        <v>-37.51566950348187</v>
+        <v>-40.5982108174511</v>
       </c>
       <c r="F94">
-        <v>1.648377259624659</v>
+        <v>-1.048032361186581</v>
       </c>
       <c r="G94">
-        <v>-8.561694297785007</v>
+        <v>-12.99963618881838</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.05356986952712</v>
       </c>
       <c r="E95">
-        <v>-39.4648447209444</v>
+        <v>-41.65886547105364</v>
       </c>
       <c r="F95">
-        <v>1.307514013781496</v>
+        <v>-1.050318655218307</v>
       </c>
       <c r="G95">
-        <v>-8.707189463690437</v>
+        <v>-13.33733500764281</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.42666460224085</v>
       </c>
       <c r="E96">
-        <v>-42.94911149260807</v>
+        <v>-43.28199282420091</v>
       </c>
       <c r="F96">
-        <v>1.202564834051216</v>
+        <v>-1.369272411624826</v>
       </c>
       <c r="G96">
-        <v>-9.457266387614187</v>
+        <v>-12.8986049600509</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.85033540811149</v>
       </c>
       <c r="E97">
-        <v>-44.5974896168221</v>
+        <v>-44.73632583718626</v>
       </c>
       <c r="F97">
-        <v>1.390948835326268</v>
+        <v>-1.376707837432354</v>
       </c>
       <c r="G97">
-        <v>-8.956417263523388</v>
+        <v>-13.19014153187574</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.3118490791585</v>
       </c>
       <c r="E98">
-        <v>-46.66400438853438</v>
+        <v>-46.68626410251908</v>
       </c>
       <c r="F98">
-        <v>0.07293180399716911</v>
+        <v>-1.833610445794478</v>
       </c>
       <c r="G98">
-        <v>-8.739917516891671</v>
+        <v>-13.08323077423051</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.78679590610103</v>
       </c>
       <c r="E99">
-        <v>-48.5762815997824</v>
+        <v>-47.42917611313644</v>
       </c>
       <c r="F99">
-        <v>0.6718430929560173</v>
+        <v>-1.679967345025434</v>
       </c>
       <c r="G99">
-        <v>-8.900459112273088</v>
+        <v>-12.89015313728914</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.30069483824768</v>
       </c>
       <c r="E100">
-        <v>-48.99248685311638</v>
+        <v>-50.16437214953233</v>
       </c>
       <c r="F100">
-        <v>0.2787057221591915</v>
+        <v>-1.96598107165963</v>
       </c>
       <c r="G100">
-        <v>-9.872547841151444</v>
+        <v>-13.39328653780204</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.79723231054886</v>
       </c>
       <c r="E101">
-        <v>-51.58886931151815</v>
+        <v>-51.40762506419065</v>
       </c>
       <c r="F101">
-        <v>0.1645475820119889</v>
+        <v>-2.268933254946271</v>
       </c>
       <c r="G101">
-        <v>-9.453793625343492</v>
+        <v>-13.23221525513434</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-20.31775879018597</v>
       </c>
       <c r="E102">
-        <v>-52.68535438358788</v>
+        <v>-53.46753845291825</v>
       </c>
       <c r="F102">
-        <v>-0.3759754021931334</v>
+        <v>-2.378229706806444</v>
       </c>
       <c r="G102">
-        <v>-9.38598703160814</v>
+        <v>-13.28640557506667</v>
       </c>
     </row>
   </sheetData>
